--- a/filters.xlsx
+++ b/filters.xlsx
@@ -5,22 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNIVERSITY\science de la matière\L2\Filters_Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNIVERSITY\science de la matière\L2\Filters_Catalog\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA5F7E-E676-4AC8-8219-ED9EC374D023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63123459-A96A-4FE1-9E4D-50F9BC92D4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="79">
   <si>
     <t>catalog_number</t>
   </si>
@@ -215,13 +216,55 @@
   </si>
   <si>
     <t>R4.txt</t>
+  </si>
+  <si>
+    <t>qrcode</t>
+  </si>
+  <si>
+    <t>qr_code</t>
+  </si>
+  <si>
+    <t>35.txt</t>
+  </si>
+  <si>
+    <t>36.txt</t>
+  </si>
+  <si>
+    <t>37.txt</t>
+  </si>
+  <si>
+    <t>38.txt</t>
+  </si>
+  <si>
+    <t>39.txt</t>
+  </si>
+  <si>
+    <t>Band Cut</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>Complex</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Sp</t>
+  </si>
+  <si>
+    <t>CBC</t>
+  </si>
+  <si>
+    <t>Complex Band Cut</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +276,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -270,11 +321,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,11 +629,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
@@ -589,7 +641,7 @@
     <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,8 +675,11 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>CONCATENATE(D2,INT(F2),"-",INT(I2))</f>
         <v>BS524-13</v>
@@ -658,10 +713,14 @@
       <c r="K2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="str">
+        <f xml:space="preserve"> CONCATENATE(B2,".png")</f>
+        <v>1.png</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <f t="shared" ref="A3:A46" si="0">CONCATENATE(D3,INT(F3),"-",INT(I3))</f>
+        <f t="shared" ref="A3:A51" si="0">CONCATENATE(D3,INT(F3),"-",INT(I3))</f>
         <v>SP453-121</v>
       </c>
       <c r="B3">
@@ -683,18 +742,22 @@
         <v>574.37</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H46" si="1">ROUND(AVERAGE(F3,G3),2)</f>
+        <f t="shared" ref="H3:H51" si="1">ROUND(AVERAGE(F3,G3),2)</f>
         <v>513.69000000000005</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I46" si="2">ROUND(ABS(F3-G3),2)</f>
+        <f t="shared" ref="I3:I51" si="2">ROUND(ABS(F3-G3),2)</f>
         <v>121.36</v>
       </c>
       <c r="K3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L51" si="3" xml:space="preserve"> CONCATENATE(B3,".png")</f>
+        <v>2.png</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>BP528-44</v>
@@ -728,8 +791,12 @@
       <c r="K4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="str">
+        <f t="shared" si="3"/>
+        <v>3.png</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>LP531-531</v>
@@ -760,8 +827,12 @@
       <c r="K5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="str">
+        <f t="shared" si="3"/>
+        <v>4.png</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>BP539-11</v>
@@ -795,8 +866,12 @@
       <c r="K6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="str">
+        <f t="shared" si="3"/>
+        <v>5.png</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>LP610-610</v>
@@ -827,8 +902,12 @@
       <c r="K7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="str">
+        <f t="shared" si="3"/>
+        <v>6.png</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>LP475-475</v>
@@ -859,31 +938,51 @@
       <c r="K8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="str">
+        <f t="shared" si="3"/>
+        <v>7.png</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>CBC479-177</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
-      <c r="H9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F9">
+        <v>479</v>
+      </c>
+      <c r="G9">
+        <v>656</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>567.5</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="K9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="str">
+        <f t="shared" si="3"/>
+        <v>8.png</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>BP625-22</v>
@@ -917,8 +1016,12 @@
       <c r="K10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" t="str">
+        <f t="shared" si="3"/>
+        <v>9.png</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>BP697-3</v>
@@ -952,8 +1055,12 @@
       <c r="K11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" t="str">
+        <f t="shared" si="3"/>
+        <v>10.png</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>SP549-549</v>
@@ -984,8 +1091,12 @@
       <c r="K12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="str">
+        <f t="shared" si="3"/>
+        <v>11.png</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>BP658-15</v>
@@ -1019,31 +1130,48 @@
       <c r="K13" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" t="str">
+        <f t="shared" si="3"/>
+        <v>12.png</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>Sp630-630</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
       <c r="E14" t="s">
         <v>13</v>
       </c>
-      <c r="H14" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F14">
+        <v>630</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>630</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="K14" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" t="str">
+        <f t="shared" si="3"/>
+        <v>13.png</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>BP532-23</v>
@@ -1077,31 +1205,51 @@
       <c r="K15" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" t="str">
+        <f t="shared" si="3"/>
+        <v>14.png</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>CBC506-184</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>77</v>
+      </c>
       <c r="E16" t="s">
         <v>13</v>
       </c>
-      <c r="H16" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F16">
+        <v>506</v>
+      </c>
+      <c r="G16">
+        <v>690</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>598</v>
       </c>
       <c r="I16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K16" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" t="str">
+        <f t="shared" si="3"/>
+        <v>15.png</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>LP545-545</v>
@@ -1132,8 +1280,12 @@
       <c r="K17" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" t="str">
+        <f t="shared" si="3"/>
+        <v>16.png</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>BP431-39</v>
@@ -1167,8 +1319,12 @@
       <c r="K18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" t="str">
+        <f t="shared" si="3"/>
+        <v>17.png</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>BP503-44</v>
@@ -1202,8 +1358,12 @@
       <c r="K19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" t="str">
+        <f t="shared" si="3"/>
+        <v>18.png</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>BP629-10</v>
@@ -1237,8 +1397,12 @@
       <c r="K20" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" t="str">
+        <f t="shared" si="3"/>
+        <v>19.png</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>BP486-10</v>
@@ -1272,8 +1436,12 @@
       <c r="K21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" t="str">
+        <f t="shared" si="3"/>
+        <v>20.png</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>BP626-22</v>
@@ -1307,31 +1475,51 @@
       <c r="K22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" t="str">
+        <f t="shared" si="3"/>
+        <v>21.png</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>BP625-23</v>
       </c>
       <c r="B23">
         <v>22</v>
       </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
       <c r="E23" t="s">
         <v>13</v>
       </c>
-      <c r="H23" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F23">
+        <v>625.75</v>
+      </c>
+      <c r="G23">
+        <v>648.86</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>637.30999999999995</v>
       </c>
       <c r="I23">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23.11</v>
       </c>
       <c r="K23" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" t="str">
+        <f t="shared" si="3"/>
+        <v>22.png</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>BP665-10</v>
@@ -1365,8 +1553,12 @@
       <c r="K24" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" t="str">
+        <f t="shared" si="3"/>
+        <v>23.png</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>BP821-16</v>
@@ -1400,8 +1592,12 @@
       <c r="K25" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" t="str">
+        <f t="shared" si="3"/>
+        <v>24.png</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>0-0</v>
@@ -1423,31 +1619,48 @@
       <c r="K26" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" t="str">
+        <f t="shared" si="3"/>
+        <v>25.png</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>LP798-798</v>
       </c>
       <c r="B27">
         <v>26</v>
       </c>
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
       <c r="E27" t="s">
         <v>13</v>
       </c>
-      <c r="H27" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F27">
+        <v>798</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>798</v>
       </c>
       <c r="I27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="K27" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" t="str">
+        <f t="shared" si="3"/>
+        <v>26.png</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>LP423-423</v>
@@ -1478,31 +1691,48 @@
       <c r="K28" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" t="str">
+        <f t="shared" si="3"/>
+        <v>27.png</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>LP423-423</v>
       </c>
       <c r="B29">
         <v>28</v>
       </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
       <c r="E29" t="s">
         <v>13</v>
       </c>
-      <c r="H29" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F29">
+        <v>423.2</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>423.2</v>
       </c>
       <c r="I29">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>423.2</v>
       </c>
       <c r="K29" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" t="str">
+        <f t="shared" si="3"/>
+        <v>28.png</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>LP796-796</v>
@@ -1533,8 +1763,12 @@
       <c r="K30" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" t="str">
+        <f t="shared" si="3"/>
+        <v>29.png</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>BP405-19</v>
@@ -1568,8 +1802,12 @@
       <c r="K31" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" t="str">
+        <f t="shared" si="3"/>
+        <v>30.png</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>LP492-492</v>
@@ -1600,8 +1838,12 @@
       <c r="K32" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" t="str">
+        <f t="shared" si="3"/>
+        <v>31.png</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>LP676-676</v>
@@ -1632,8 +1874,12 @@
       <c r="K33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" t="str">
+        <f t="shared" si="3"/>
+        <v>32.png</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>SP500-500</v>
@@ -1664,284 +1910,1122 @@
       <c r="K34" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L34" t="str">
+        <f t="shared" si="3"/>
+        <v>33.png</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>SP531-531</v>
       </c>
       <c r="B35">
         <v>34</v>
       </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
       <c r="E35" t="s">
         <v>13</v>
       </c>
-      <c r="H35" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F35">
+        <v>531.36</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>531.36</v>
       </c>
       <c r="I35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>531.36</v>
       </c>
       <c r="K35" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" t="str">
+        <f t="shared" si="3"/>
+        <v>34.png</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>C403-403</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>75</v>
+      </c>
       <c r="E36" t="s">
         <v>13</v>
       </c>
-      <c r="H36" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F36">
+        <v>403</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>403</v>
       </c>
       <c r="I36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="K36" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" t="str">
+        <f t="shared" si="3"/>
+        <v>35.png</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>LP560-560</v>
       </c>
       <c r="B37">
         <v>36</v>
       </c>
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
       <c r="E37" t="s">
         <v>13</v>
       </c>
-      <c r="H37" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F37">
+        <v>560</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>560</v>
       </c>
       <c r="I37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="K37" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L37" t="str">
+        <f t="shared" si="3"/>
+        <v>36.png</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>BC520-166</v>
       </c>
       <c r="B38">
         <v>37</v>
       </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" t="s">
+        <v>73</v>
+      </c>
       <c r="E38" t="s">
         <v>13</v>
       </c>
-      <c r="H38" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F38">
+        <v>520</v>
+      </c>
+      <c r="G38">
+        <v>686.6</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>603.29999999999995</v>
       </c>
       <c r="I38">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>166.6</v>
       </c>
       <c r="K38" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L38" t="str">
+        <f t="shared" si="3"/>
+        <v>37.png</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>BC527-182</v>
       </c>
       <c r="B39">
         <v>38</v>
       </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" t="s">
+        <v>73</v>
+      </c>
       <c r="E39" t="s">
         <v>13</v>
       </c>
-      <c r="H39" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F39">
+        <v>527.4</v>
+      </c>
+      <c r="G39">
+        <v>710</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>618.70000000000005</v>
       </c>
       <c r="I39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>182.6</v>
       </c>
       <c r="K39" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" t="str">
+        <f t="shared" si="3"/>
+        <v>38.png</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>LP490-490</v>
       </c>
       <c r="B40">
         <v>39</v>
       </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>22</v>
+      </c>
       <c r="E40" t="s">
         <v>13</v>
       </c>
-      <c r="H40" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F40">
+        <v>490</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>490</v>
       </c>
       <c r="I40">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="K40" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L40" t="str">
+        <f t="shared" si="3"/>
+        <v>39.png</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>BC442-46</v>
       </c>
       <c r="B41">
         <v>40</v>
       </c>
+      <c r="C41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="s">
+        <v>73</v>
+      </c>
       <c r="E41" t="s">
         <v>13</v>
       </c>
-      <c r="H41" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F41">
+        <v>442.8</v>
+      </c>
+      <c r="G41">
+        <v>489.1</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>465.95</v>
       </c>
       <c r="I41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>46.3</v>
       </c>
       <c r="K41" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L41" t="str">
+        <f t="shared" si="3"/>
+        <v>40.png</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>LP490-490</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" t="s">
+        <v>22</v>
+      </c>
       <c r="E42" t="s">
         <v>13</v>
       </c>
-      <c r="H42" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F42">
+        <v>490.1</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>490.1</v>
       </c>
       <c r="I42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>490.1</v>
       </c>
       <c r="K42" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L42" t="str">
+        <f t="shared" si="3"/>
+        <v>41.png</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>BC567-34</v>
       </c>
       <c r="B43">
         <v>42</v>
       </c>
+      <c r="C43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" t="s">
+        <v>73</v>
+      </c>
       <c r="E43" t="s">
         <v>13</v>
       </c>
-      <c r="H43" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F43">
+        <v>567.9</v>
+      </c>
+      <c r="G43">
+        <v>602.6</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>585.25</v>
       </c>
       <c r="I43">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="K43" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L43" t="str">
+        <f t="shared" si="3"/>
+        <v>42.png</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>C508-170</v>
       </c>
       <c r="B44">
         <v>43</v>
       </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" t="s">
+        <v>75</v>
+      </c>
       <c r="E44" t="s">
         <v>13</v>
       </c>
-      <c r="H44" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F44">
+        <v>508</v>
+      </c>
+      <c r="G44">
+        <v>678.5</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>593.25</v>
       </c>
       <c r="I44">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>170.5</v>
       </c>
       <c r="K44" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L44" t="str">
+        <f t="shared" si="3"/>
+        <v>43.png</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>SP648-648</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
       <c r="E45" t="s">
         <v>13</v>
       </c>
-      <c r="H45" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F45">
+        <v>648.70000000000005</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>648.70000000000005</v>
       </c>
       <c r="I45">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>648.70000000000005</v>
       </c>
       <c r="K45" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L45" t="str">
+        <f t="shared" si="3"/>
+        <v>44.png</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f t="shared" si="0"/>
-        <v>0-0</v>
+        <v>BC470-231</v>
       </c>
       <c r="B46">
         <v>45</v>
       </c>
+      <c r="C46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" t="s">
+        <v>73</v>
+      </c>
       <c r="E46" t="s">
         <v>13</v>
       </c>
-      <c r="H46" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+      <c r="F46">
+        <v>470.5</v>
+      </c>
+      <c r="G46">
+        <v>701.6</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>586.04999999999995</v>
       </c>
       <c r="I46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>231.1</v>
       </c>
       <c r="K46" t="s">
         <v>64</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="3"/>
+        <v>45.png</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="str">
+        <f t="shared" si="0"/>
+        <v>BP775-10</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47">
+        <v>775.35</v>
+      </c>
+      <c r="G47">
+        <v>786.11</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>780.73</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>10.76</v>
+      </c>
+      <c r="K47" t="s">
+        <v>67</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="3"/>
+        <v>46.png</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="str">
+        <f t="shared" si="0"/>
+        <v>BP449-45</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48">
+        <v>449</v>
+      </c>
+      <c r="G48">
+        <v>494.57</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>471.79</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>45.57</v>
+      </c>
+      <c r="K48" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="3"/>
+        <v>47.png</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="str">
+        <f t="shared" si="0"/>
+        <v>LP518-518</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49">
+        <v>518.75</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>518.75</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>518.75</v>
+      </c>
+      <c r="K49" t="s">
+        <v>69</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="3"/>
+        <v>48.png</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="str">
+        <f t="shared" si="0"/>
+        <v>BP586-39</v>
+      </c>
+      <c r="B50">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50">
+        <v>586.6</v>
+      </c>
+      <c r="G50">
+        <v>625.70000000000005</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>606.15</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>39.1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>70</v>
+      </c>
+      <c r="L50" t="str">
+        <f t="shared" si="3"/>
+        <v>49.png</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="str">
+        <f t="shared" si="0"/>
+        <v>LP491-491</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51">
+        <v>491.5</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>491.5</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>491.5</v>
+      </c>
+      <c r="K51" t="s">
+        <v>71</v>
+      </c>
+      <c r="L51" t="str">
+        <f t="shared" si="3"/>
+        <v>50.png</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ADC2F2-DF27-4DE7-B881-9971BF0D7323}">
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <f xml:space="preserve"> Sheet1!A2</f>
+        <v>BS524-13</v>
+      </c>
+      <c r="B2" t="str">
+        <f xml:space="preserve"> Sheet1!L2</f>
+        <v>1.png</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f xml:space="preserve"> Sheet1!A3</f>
+        <v>SP453-121</v>
+      </c>
+      <c r="B3" t="str">
+        <f xml:space="preserve"> Sheet1!L3</f>
+        <v>2.png</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f xml:space="preserve"> Sheet1!A4</f>
+        <v>BP528-44</v>
+      </c>
+      <c r="B4" t="str">
+        <f xml:space="preserve"> Sheet1!L4</f>
+        <v>3.png</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f xml:space="preserve"> Sheet1!A5</f>
+        <v>LP531-531</v>
+      </c>
+      <c r="B5" t="str">
+        <f xml:space="preserve"> Sheet1!L5</f>
+        <v>4.png</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f xml:space="preserve"> Sheet1!A6</f>
+        <v>BP539-11</v>
+      </c>
+      <c r="B6" t="str">
+        <f xml:space="preserve"> Sheet1!L6</f>
+        <v>5.png</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f xml:space="preserve"> Sheet1!A7</f>
+        <v>LP610-610</v>
+      </c>
+      <c r="B7" t="str">
+        <f xml:space="preserve"> Sheet1!L7</f>
+        <v>6.png</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f xml:space="preserve"> Sheet1!A8</f>
+        <v>LP475-475</v>
+      </c>
+      <c r="B8" t="str">
+        <f xml:space="preserve"> Sheet1!L8</f>
+        <v>7.png</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f xml:space="preserve"> Sheet1!A9</f>
+        <v>CBC479-177</v>
+      </c>
+      <c r="B9" t="str">
+        <f xml:space="preserve"> Sheet1!L9</f>
+        <v>8.png</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f xml:space="preserve"> Sheet1!A10</f>
+        <v>BP625-22</v>
+      </c>
+      <c r="B10" t="str">
+        <f xml:space="preserve"> Sheet1!L10</f>
+        <v>9.png</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f xml:space="preserve"> Sheet1!A11</f>
+        <v>BP697-3</v>
+      </c>
+      <c r="B11" t="str">
+        <f xml:space="preserve"> Sheet1!L11</f>
+        <v>10.png</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f xml:space="preserve"> Sheet1!A12</f>
+        <v>SP549-549</v>
+      </c>
+      <c r="B12" t="str">
+        <f xml:space="preserve"> Sheet1!L12</f>
+        <v>11.png</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f xml:space="preserve"> Sheet1!A13</f>
+        <v>BP658-15</v>
+      </c>
+      <c r="B13" t="str">
+        <f xml:space="preserve"> Sheet1!L13</f>
+        <v>12.png</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f xml:space="preserve"> Sheet1!A14</f>
+        <v>Sp630-630</v>
+      </c>
+      <c r="B14" t="str">
+        <f xml:space="preserve"> Sheet1!L14</f>
+        <v>13.png</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f xml:space="preserve"> Sheet1!A15</f>
+        <v>BP532-23</v>
+      </c>
+      <c r="B15" t="str">
+        <f xml:space="preserve"> Sheet1!L15</f>
+        <v>14.png</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f xml:space="preserve"> Sheet1!A16</f>
+        <v>CBC506-184</v>
+      </c>
+      <c r="B16" t="str">
+        <f xml:space="preserve"> Sheet1!L16</f>
+        <v>15.png</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f xml:space="preserve"> Sheet1!A17</f>
+        <v>LP545-545</v>
+      </c>
+      <c r="B17" t="str">
+        <f xml:space="preserve"> Sheet1!L17</f>
+        <v>16.png</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f xml:space="preserve"> Sheet1!A18</f>
+        <v>BP431-39</v>
+      </c>
+      <c r="B18" t="str">
+        <f xml:space="preserve"> Sheet1!L18</f>
+        <v>17.png</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f xml:space="preserve"> Sheet1!A19</f>
+        <v>BP503-44</v>
+      </c>
+      <c r="B19" t="str">
+        <f xml:space="preserve"> Sheet1!L19</f>
+        <v>18.png</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f xml:space="preserve"> Sheet1!A20</f>
+        <v>BP629-10</v>
+      </c>
+      <c r="B20" t="str">
+        <f xml:space="preserve"> Sheet1!L20</f>
+        <v>19.png</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f xml:space="preserve"> Sheet1!A21</f>
+        <v>BP486-10</v>
+      </c>
+      <c r="B21" t="str">
+        <f xml:space="preserve"> Sheet1!L21</f>
+        <v>20.png</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f xml:space="preserve"> Sheet1!A22</f>
+        <v>BP626-22</v>
+      </c>
+      <c r="B22" t="str">
+        <f xml:space="preserve"> Sheet1!L22</f>
+        <v>21.png</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f xml:space="preserve"> Sheet1!A23</f>
+        <v>BP625-23</v>
+      </c>
+      <c r="B23" t="str">
+        <f xml:space="preserve"> Sheet1!L23</f>
+        <v>22.png</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f xml:space="preserve"> Sheet1!A24</f>
+        <v>BP665-10</v>
+      </c>
+      <c r="B24" t="str">
+        <f xml:space="preserve"> Sheet1!L24</f>
+        <v>23.png</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f xml:space="preserve"> Sheet1!A25</f>
+        <v>BP821-16</v>
+      </c>
+      <c r="B25" t="str">
+        <f xml:space="preserve"> Sheet1!L25</f>
+        <v>24.png</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f xml:space="preserve"> Sheet1!A26</f>
+        <v>0-0</v>
+      </c>
+      <c r="B26" t="str">
+        <f xml:space="preserve"> Sheet1!L26</f>
+        <v>25.png</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f xml:space="preserve"> Sheet1!A27</f>
+        <v>LP798-798</v>
+      </c>
+      <c r="B27" t="str">
+        <f xml:space="preserve"> Sheet1!L27</f>
+        <v>26.png</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <f xml:space="preserve"> Sheet1!A28</f>
+        <v>LP423-423</v>
+      </c>
+      <c r="B28" t="str">
+        <f xml:space="preserve"> Sheet1!L28</f>
+        <v>27.png</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <f xml:space="preserve"> Sheet1!A29</f>
+        <v>LP423-423</v>
+      </c>
+      <c r="B29" t="str">
+        <f xml:space="preserve"> Sheet1!L29</f>
+        <v>28.png</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <f xml:space="preserve"> Sheet1!A30</f>
+        <v>LP796-796</v>
+      </c>
+      <c r="B30" t="str">
+        <f xml:space="preserve"> Sheet1!L30</f>
+        <v>29.png</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <f xml:space="preserve"> Sheet1!A31</f>
+        <v>BP405-19</v>
+      </c>
+      <c r="B31" t="str">
+        <f xml:space="preserve"> Sheet1!L31</f>
+        <v>30.png</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="str">
+        <f xml:space="preserve"> Sheet1!A32</f>
+        <v>LP492-492</v>
+      </c>
+      <c r="B32" t="str">
+        <f xml:space="preserve"> Sheet1!L32</f>
+        <v>31.png</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f xml:space="preserve"> Sheet1!A33</f>
+        <v>LP676-676</v>
+      </c>
+      <c r="B33" t="str">
+        <f xml:space="preserve"> Sheet1!L33</f>
+        <v>32.png</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f xml:space="preserve"> Sheet1!A34</f>
+        <v>SP500-500</v>
+      </c>
+      <c r="B34" t="str">
+        <f xml:space="preserve"> Sheet1!L34</f>
+        <v>33.png</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f xml:space="preserve"> Sheet1!A35</f>
+        <v>SP531-531</v>
+      </c>
+      <c r="B35" t="str">
+        <f xml:space="preserve"> Sheet1!L35</f>
+        <v>34.png</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f xml:space="preserve"> Sheet1!A36</f>
+        <v>C403-403</v>
+      </c>
+      <c r="B36" t="str">
+        <f xml:space="preserve"> Sheet1!L36</f>
+        <v>35.png</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f xml:space="preserve"> Sheet1!A37</f>
+        <v>LP560-560</v>
+      </c>
+      <c r="B37" t="str">
+        <f xml:space="preserve"> Sheet1!L37</f>
+        <v>36.png</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f xml:space="preserve"> Sheet1!A38</f>
+        <v>BC520-166</v>
+      </c>
+      <c r="B38" t="str">
+        <f xml:space="preserve"> Sheet1!L38</f>
+        <v>37.png</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f xml:space="preserve"> Sheet1!A39</f>
+        <v>BC527-182</v>
+      </c>
+      <c r="B39" t="str">
+        <f xml:space="preserve"> Sheet1!L39</f>
+        <v>38.png</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f xml:space="preserve"> Sheet1!A40</f>
+        <v>LP490-490</v>
+      </c>
+      <c r="B40" t="str">
+        <f xml:space="preserve"> Sheet1!L40</f>
+        <v>39.png</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
+        <f xml:space="preserve"> Sheet1!A41</f>
+        <v>BC442-46</v>
+      </c>
+      <c r="B41" t="str">
+        <f xml:space="preserve"> Sheet1!L41</f>
+        <v>40.png</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
+        <f xml:space="preserve"> Sheet1!A42</f>
+        <v>LP490-490</v>
+      </c>
+      <c r="B42" t="str">
+        <f xml:space="preserve"> Sheet1!L42</f>
+        <v>41.png</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f xml:space="preserve"> Sheet1!A43</f>
+        <v>BC567-34</v>
+      </c>
+      <c r="B43" t="str">
+        <f xml:space="preserve"> Sheet1!L43</f>
+        <v>42.png</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="str">
+        <f xml:space="preserve"> Sheet1!A44</f>
+        <v>C508-170</v>
+      </c>
+      <c r="B44" t="str">
+        <f xml:space="preserve"> Sheet1!L44</f>
+        <v>43.png</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
+        <f xml:space="preserve"> Sheet1!A45</f>
+        <v>SP648-648</v>
+      </c>
+      <c r="B45" t="str">
+        <f xml:space="preserve"> Sheet1!L45</f>
+        <v>44.png</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="str">
+        <f xml:space="preserve"> Sheet1!A46</f>
+        <v>BC470-231</v>
+      </c>
+      <c r="B46" t="str">
+        <f xml:space="preserve"> Sheet1!L46</f>
+        <v>45.png</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>